--- a/pricing/output/商务洽谈折扣总表.xlsx
+++ b/pricing/output/商务洽谈折扣总表.xlsx
@@ -8,8 +8,8 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_说明" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_报价解析汇总" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_报价解析汇总" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_说明" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_商务总表-生文" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_交叉模型-生文" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="20_商务总表-生图" sheetId="6" state="visible" r:id="rId6"/>
@@ -993,384 +993,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="88" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="7" t="inlineStr">
-        <is>
-          <t>文件名</t>
-        </is>
-      </c>
-      <c r="B1" s="8" t="inlineStr">
-        <is>
-          <t>商务洽谈折扣总表.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="7" t="inlineStr">
-        <is>
-          <t>形态</t>
-        </is>
-      </c>
-      <c r="B2" s="8" t="inlineStr">
-        <is>
-          <t>一本总册 · 9 Sheet（含「更新」）；后台分册下载另议</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="7" t="inlineStr">
-        <is>
-          <t>生成·商务</t>
-        </is>
-      </c>
-      <c r="B3" s="8" t="inlineStr">
-        <is>
-          <t>commercial-billing/scripts/rebuild_discount_tier_workbook.py</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>生成·解析/外发</t>
-        </is>
-      </c>
-      <c r="B4" s="8" t="inlineStr">
-        <is>
-          <t>pricing/scripts/build_outward_quote_standard.py（回写 01 + 外发 xlsx）</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>SOP</t>
-        </is>
-      </c>
-      <c r="B5" s="8" t="inlineStr">
-        <is>
-          <t>discount-tier-workbook-sop.md</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
-      <c r="B6" s="8" t="inlineStr">
-        <is>
-          <t>变更日志：日期 / 分类 / 更新说明 / 备注；新→旧</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>01_报价解析汇总</t>
-        </is>
-      </c>
-      <c r="B7" s="8" t="inlineStr">
-        <is>
-          <t>报价依据：全量解析 / 原价专项 / 停用更低进价（外发脚本回写）</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>10_商务总表-生文</t>
-        </is>
-      </c>
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>生文 · 成本族 × 对内阶梯（含GM）× 模型清单</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>11_交叉模型-生文</t>
-        </is>
-      </c>
-      <c r="B9" s="8" t="inlineStr">
-        <is>
-          <t>生文 · 跨折同名 · 优先级/权重 · 推荐成本折</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>20_商务总表-生图</t>
-        </is>
-      </c>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>生图 · 成本族 × 对内阶梯 × 模型清单</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>21_交叉模型-生图</t>
-        </is>
-      </c>
-      <c r="B11" s="8" t="inlineStr">
-        <is>
-          <t>生图 · 跨折同名 · 推荐成本折</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>30_商务总表-生视频</t>
-        </is>
-      </c>
-      <c r="B12" s="8" t="inlineStr">
-        <is>
-          <t>生视频 · 成本族 × 对内阶梯 × 模型清单</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>31_交叉模型-生视频</t>
-        </is>
-      </c>
-      <c r="B13" s="8" t="inlineStr">
-        <is>
-          <t>生视频 · 跨折同名 · 推荐成本折</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>外发文件</t>
-        </is>
-      </c>
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t>pricing/output/Trinity模型报价表.xlsx（01_生文/02_生图/03_生视频，整本可发）</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>档名</t>
-        </is>
-      </c>
-      <c r="B15" s="8" t="inlineStr">
-        <is>
-          <t>对内五档：$1k/$5k/$10k/$30k/$50k（Plus…Enterprise）｜对外三档：$5k/$10k/$50k（表头「对外·」）</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>生文已导入</t>
-        </is>
-      </c>
-      <c r="B16" s="8" t="inlineStr">
-        <is>
-          <t>0.026:2 · 0.0277:7 · 0.0693:7 · 0.32:1 · 0.3516:2 · 0.40:2 · 0.4643:1 · 0.50:1 · 0.60:12 · 0.65:14 · 0.70:24 · 0.75:14 · 0.78:17 · 1.0:15</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>生文交叉模型数</t>
-        </is>
-      </c>
-      <c r="B17" s="8" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>生图已导入</t>
-        </is>
-      </c>
-      <c r="B18" s="8" t="inlineStr">
-        <is>
-          <t>0.1143:2 · 0.1429:1 · 0.55:1 · 0.65:1 · 0.75:3</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t>生图交叉模型数</t>
-        </is>
-      </c>
-      <c r="B19" s="8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>生视频已导入</t>
-        </is>
-      </c>
-      <c r="B20" s="8" t="inlineStr">
-        <is>
-          <t>0.32:1 · 0.34:1 · 0.40:1 · 0.55:8 · 0.60:3 · 0.64:1 · 0.70:2 · 0.75:4 · 0.85:3 · 1.0:3</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t>生视频交叉模型数</t>
-        </is>
-      </c>
-      <c r="B21" s="8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t>线路源·生文</t>
-        </is>
-      </c>
-      <c r="B22" s="8" t="inlineStr">
-        <is>
-          <t>pricing/input/routes-live/text-enabled.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="7" t="inlineStr">
-        <is>
-          <t>线路源索引·生文</t>
-        </is>
-      </c>
-      <c r="B23" s="8" t="inlineStr">
-        <is>
-          <t>text-enabled.xlsx（单文件·折扣分族）· 0.26折=2；0.277折=7；0.693折=7；3.2折=1；3.516折=2；4折=2；4.643折=1；5折=1；6折=12；6.5折=14；7折=24；7.5折=14；7.8折=17；原价=15</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="7" t="inlineStr">
-        <is>
-          <t>线路源·生图</t>
-        </is>
-      </c>
-      <c r="B24" s="8" t="inlineStr">
-        <is>
-          <t>pricing/input/routes-live/image-enabled.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="7" t="inlineStr">
-        <is>
-          <t>线路源索引·生图</t>
-        </is>
-      </c>
-      <c r="B25" s="8" t="inlineStr">
-        <is>
-          <t>image-enabled.xlsx（单文件·折扣分族）· 1.143折=2；1.429折=1；5.5折=1；6.5折=1；7.5折=3</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="7" t="inlineStr">
-        <is>
-          <t>线路源·生视频</t>
-        </is>
-      </c>
-      <c r="B26" s="8" t="inlineStr">
-        <is>
-          <t>pricing/input/routes-live/video-enabled.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="7" t="inlineStr">
-        <is>
-          <t>线路源索引·生视频</t>
-        </is>
-      </c>
-      <c r="B27" s="8" t="inlineStr">
-        <is>
-          <t>video-enabled.xlsx（单文件·折扣分族）· 3.2折=1；3.4折=1；4折=1；5.5折=8；6折=3；6.4折=1；7折=2；7.5折=4；8.5折=3；原价=3</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="7" t="inlineStr">
-        <is>
-          <t>分族方式</t>
-        </is>
-      </c>
-      <c r="B28" s="8" t="inlineStr">
-        <is>
-          <t>现网导出·折扣列自动分族</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="7" t="inlineStr">
-        <is>
-          <t>不含</t>
-        </is>
-      </c>
-      <c r="B29" s="8" t="inlineStr">
-        <is>
-          <t>各折扣 src_* 整表；原料只归档 input</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="45" t="inlineStr">
-        <is>
-          <t>01最近回写</t>
-        </is>
-      </c>
-      <c r="B30" s="54" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:L239"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -12029,6 +11651,384 @@
     <mergeCell ref="B5:F5"/>
     <mergeCell ref="A162:L162"/>
   </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B30"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="88" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>文件名</t>
+        </is>
+      </c>
+      <c r="B1" s="8" t="inlineStr">
+        <is>
+          <t>商务洽谈折扣总表.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>形态</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>一本总册 · 9 Sheet（含「更新」）；后台分册下载另议</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>生成·商务</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>commercial-billing/scripts/rebuild_discount_tier_workbook.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>生成·解析/外发</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>pricing/scripts/build_outward_quote_standard.py（回写 01 + 外发 xlsx）</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>SOP</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>discount-tier-workbook-sop.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>更新</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>变更日志：日期 / 分类 / 更新说明 / 备注；新→旧</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>01_报价解析汇总</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>报价依据：全量解析 / 原价专项 / 停用更低进价（外发脚本回写）</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>10_商务总表-生文</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>生文 · 成本族 × 对内阶梯（含GM）× 模型清单</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>11_交叉模型-生文</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>生文 · 跨折同名 · 优先级/权重 · 推荐成本折</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>20_商务总表-生图</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>生图 · 成本族 × 对内阶梯 × 模型清单</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>21_交叉模型-生图</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>生图 · 跨折同名 · 推荐成本折</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>30_商务总表-生视频</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>生视频 · 成本族 × 对内阶梯 × 模型清单</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>31_交叉模型-生视频</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>生视频 · 跨折同名 · 推荐成本折</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>外发文件</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>pricing/output/Trinity模型报价表.xlsx（01_生文/02_生图/03_生视频，整本可发）</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>档名</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>对内五档：$1k/$5k/$10k/$30k/$50k（Plus…Enterprise）｜对外三档：$5k/$10k/$50k（表头「对外·」）</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>生文已导入</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>0.026:2 · 0.0277:7 · 0.0693:7 · 0.32:1 · 0.3516:2 · 0.40:2 · 0.4643:1 · 0.50:1 · 0.60:12 · 0.65:14 · 0.70:24 · 0.75:14 · 0.78:17 · 1.0:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>生文交叉模型数</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>生图已导入</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>0.1143:2 · 0.1429:1 · 0.55:1 · 0.65:1 · 0.75:3</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>生图交叉模型数</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>生视频已导入</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>0.32:1 · 0.34:1 · 0.40:1 · 0.55:8 · 0.60:3 · 0.64:1 · 0.70:2 · 0.75:4 · 0.85:3 · 1.0:3</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>生视频交叉模型数</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>线路源·生文</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>pricing/input/routes-live/text-enabled.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>线路源索引·生文</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>text-enabled.xlsx（单文件·折扣分族）· 0.26折=2；0.277折=7；0.693折=7；3.2折=1；3.516折=2；4折=2；4.643折=1；5折=1；6折=12；6.5折=14；7折=24；7.5折=14；7.8折=17；原价=15</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>线路源·生图</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>pricing/input/routes-live/image-enabled.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>线路源索引·生图</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>image-enabled.xlsx（单文件·折扣分族）· 1.143折=2；1.429折=1；5.5折=1；6.5折=1；7.5折=3</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>线路源·生视频</t>
+        </is>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>pricing/input/routes-live/video-enabled.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>线路源索引·生视频</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>video-enabled.xlsx（单文件·折扣分族）· 3.2折=1；3.4折=1；4折=1；5.5折=8；6折=3；6.4折=1；7折=2；7.5折=4；8.5折=3；原价=3</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>分族方式</t>
+        </is>
+      </c>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>现网导出·折扣列自动分族</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>不含</t>
+        </is>
+      </c>
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t>各折扣 src_* 整表；原料只归档 input</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="45" t="inlineStr">
+        <is>
+          <t>01最近回写</t>
+        </is>
+      </c>
+      <c r="B30" s="54" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
